--- a/Result/profitability/3324.xlsx
+++ b/Result/profitability/3324.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.79</v>
       </c>
       <c r="M2" t="n">
-        <v>6.22125</v>
+        <v>6.96875</v>
       </c>
       <c r="N2" t="n">
-        <v>25.23375</v>
+        <v>25.49375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>5.54375</v>
+        <v>6.19</v>
       </c>
       <c r="N3" t="n">
-        <v>22.8125</v>
+        <v>23.55375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8775</v>
+        <v>5.47125</v>
       </c>
       <c r="N4" t="n">
-        <v>21.3025</v>
+        <v>21.435</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0325</v>
+        <v>5.114999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>19.13</v>
+        <v>19.41625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.745</v>
+        <v>3.71375</v>
       </c>
       <c r="N6" t="n">
-        <v>17.14</v>
+        <v>16.97125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>2.24125</v>
+        <v>2.26625</v>
       </c>
       <c r="N7" t="n">
-        <v>14.11375</v>
+        <v>14.37</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0125</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>12.295</v>
+        <v>12.14</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8700</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6228</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2472</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1390</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-73</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1317</v>
+      </c>
+      <c r="K75" t="n">
+        <v>969</v>
+      </c>
+      <c r="L75" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.62125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.0675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1744647105471847</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.239999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04180714767363447</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.948571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.290000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08763872942977424</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
